--- a/vlearn-app/public/quiz_excel/Day_14_AI Evaluation _ Benchmarking/Day_14_Phan_03_18_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_14_AI Evaluation _ Benchmarking/Day_14_Phan_03_18_Cau.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -744,7 +744,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: ‘Tất cả k lần’ dùng p^k, không phải pass@k.</t>
+          <t>Xác suất pass^3 cho cả 3 run liên tiếp độc lập thành công với p=0,8: pass^3 = p^3 = 0,8^3 = 0,512 = 51,2%.</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -792,7 +792,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng complement của việc cả ba lần đều fail.</t>
+          <t>Xác suất pass@3 (ít nhất một lần thành công trong 3 lần thử độc lập): pass@3 = 1 - (1 - p)^3 = 1 - (1 - 0,8)^3 = 1 - 0,2^3 = 1 - 0,008 = 0,992 = 99,2%.</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1216,7 +1216,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính update từ chênh lệch observed và expected.</t>
+          <t>Công thức Elo: R'_A = R_A + K * (observed - expected) = 1200 + 32 * (1 - 0,5) = 1200 + 16 = 1216.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1317,7 +1317,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là số cặp đã chạy đủ hai order.</t>
+          <t>Flip rate khi swap vị trí cặp câu trả lời A/B và B/A: (6 cặp đổi winner / 20 cặp đã thử) * 100% = 30%.</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1461,7 +1461,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số gồm toàn bộ case FAIL theo human gold.</t>
+          <t>True Positive Rate (TPR / Sensitivity / Recall) trên class FAIL: TP / (TP + FN) = 30 / (30 + 10) = 30 / 40 = 0,75 = 75%.</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1509,7 +1509,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính J rồi chia observed delta cho J.</t>
+          <t>Youden's J = TPR + TNR - 1 = 0,8 + 0,9 - 1 = 0,7. Công thức quan hệ observed delta ≈ J * true delta =&gt; true delta ≈ observed delta / J = 7 / 0,7 = 10 điểm phần trăm.</t>
         </is>
       </c>
     </row>
